--- a/data/trans_orig/P33_1_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P33_1_2023-Edad-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de horas que duerme habitualmente al día entre semana</t>
+          <t>Número medio de horas que duerme habitualmente al día entre semana (tasa de respuesta: 97,4%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,54; 7,89</t>
+          <t>7,53; 7,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,36; 7,68</t>
+          <t>7,36; 7,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,51; 7,75</t>
+          <t>7,52; 7,75</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,16; 7,4</t>
+          <t>7,16; 7,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,12; 7,34</t>
+          <t>7,11; 7,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,17; 7,35</t>
+          <t>7,17; 7,34</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,01; 7,19</t>
+          <t>7,0; 7,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,02; 7,15</t>
+          <t>7,02; 7,14</t>
         </is>
       </c>
     </row>
@@ -726,12 +726,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,89; 7,03</t>
+          <t>6,9; 7,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,94; 7,47</t>
+          <t>6,94; 7,49</t>
         </is>
       </c>
     </row>
@@ -771,12 +771,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,88; 7,05</t>
+          <t>6,88; 7,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,66; 6,82</t>
+          <t>6,66; 6,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -826,12 +826,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,2; 6,83</t>
+          <t>6,22; 6,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,36; 6,9</t>
+          <t>6,33; 6,89</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,87; 7,11</t>
+          <t>6,87; 7,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,81; 6,97</t>
+          <t>6,82; 6,97</t>
         </is>
       </c>
     </row>
@@ -926,12 +926,12 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,77; 7,01</t>
+          <t>6,75; 7,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,97; 7,14</t>
+          <t>6,97; 7,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33_1_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P33_1_2023-Edad-trans_orig.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>7,74</t>
+          <t>7,69</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7,64</t>
+          <t>7,61</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,53; 7,9</t>
+          <t>7,54; 7,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,52; 7,75</t>
+          <t>7,5; 7,73</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,28</t>
+          <t>7,31</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7,23</t>
+          <t>7,27</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,25</t>
+          <t>7,29</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,16; 7,39</t>
+          <t>7,19; 7,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,11; 7,35</t>
+          <t>7,16; 7,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,17; 7,34</t>
+          <t>7,21; 7,36</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>7,1</t>
+          <t>7,12</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7,07</t>
+          <t>7,06</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,08</t>
+          <t>7,09</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,0; 7,19</t>
+          <t>7,04; 7,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,99; 7,14</t>
+          <t>6,99; 7,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,02; 7,14</t>
+          <t>7,03; 7,15</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>7,25</t>
+          <t>6,99</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7,12</t>
+          <t>6,97</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,93; 7,63</t>
+          <t>6,9; 7,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,9; 7,03</t>
+          <t>6,89; 7,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,94; 7,49</t>
+          <t>6,92; 7,03</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6,73</t>
+          <t>6,74</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,88; 7,04</t>
+          <t>6,89; 7,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,79; 6,91</t>
+          <t>6,8; 6,91</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>6,94</t>
+          <t>6,95</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6,53</t>
+          <t>6,81</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6,68</t>
+          <t>6,88</t>
         </is>
       </c>
     </row>
@@ -821,17 +821,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,84; 7,04</t>
+          <t>6,85; 7,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,22; 6,83</t>
+          <t>6,72; 6,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,33; 6,89</t>
+          <t>6,82; 6,94</t>
         </is>
       </c>
     </row>
@@ -848,17 +848,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>6,99</t>
+          <t>7,0</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6,83</t>
+          <t>6,85</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,89</t>
+          <t>6,91</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,87; 7,12</t>
+          <t>6,87; 7,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,73; 6,93</t>
+          <t>6,76; 6,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,82; 6,97</t>
+          <t>6,83; 6,99</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7,18</t>
+          <t>7,13</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6,94</t>
+          <t>7,01</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -921,17 +921,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,1; 7,37</t>
+          <t>7,09; 7,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,75; 7,01</t>
+          <t>6,97; 7,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6,97; 7,15</t>
+          <t>7,04; 7,09</t>
         </is>
       </c>
     </row>
